--- a/JIRA Import Template.xlsx
+++ b/JIRA Import Template.xlsx
@@ -5,27 +5,29 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shawn\OneDrive\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D794F6F-2F32-4E78-9E43-F05C43938782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7238A1D7-CD8F-4615-A1A7-EE68055CFD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{C8A0A42C-1953-43D3-B390-7B7805DF41AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C8A0A42C-1953-43D3-B390-7B7805DF41AC}"/>
   </bookViews>
   <sheets>
     <sheet name="JIRA Basics" sheetId="11" r:id="rId1"/>
-    <sheet name="JIRA Import Template" sheetId="1" r:id="rId2"/>
-    <sheet name="Drop Downs" sheetId="7" state="hidden" r:id="rId3"/>
-    <sheet name="JIRA Fields" sheetId="2" r:id="rId4"/>
-    <sheet name="Sample .csv" sheetId="3" r:id="rId5"/>
-    <sheet name="How to upload a Space to JIRA" sheetId="4" r:id="rId6"/>
-    <sheet name="Sample Configuration File" sheetId="9" r:id="rId7"/>
-    <sheet name="Sample Import Log" sheetId="10" r:id="rId8"/>
-    <sheet name="Upload to Data Mapping" sheetId="8" r:id="rId9"/>
-    <sheet name="Using Notepad Plus" sheetId="6" r:id="rId10"/>
+    <sheet name="JIRA Fields" sheetId="2" r:id="rId2"/>
+    <sheet name="JQL" sheetId="13" r:id="rId3"/>
+    <sheet name="JIRA Import Template" sheetId="1" r:id="rId4"/>
+    <sheet name="Drop Downs" sheetId="7" state="hidden" r:id="rId5"/>
+    <sheet name="Sample .csv" sheetId="3" r:id="rId6"/>
+    <sheet name="How to upload a Space to JIRA" sheetId="4" r:id="rId7"/>
+    <sheet name="Sample Configuration File" sheetId="9" r:id="rId8"/>
+    <sheet name="Sample Import Log" sheetId="10" r:id="rId9"/>
+    <sheet name="Upload to Data Mapping" sheetId="8" r:id="rId10"/>
+    <sheet name="Using Notepad Plus" sheetId="6" r:id="rId11"/>
+    <sheet name="JIRA Project Management Quiz" sheetId="12" state="hidden" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Upload to Data Mapping'!$U$2:$AA$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Upload to Data Mapping'!$U$2:$AA$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="566">
   <si>
     <t>SUMMARY</t>
   </si>
@@ -1046,9 +1048,6 @@
     <t>After importing the .CSV headers, you may need to further define further values.</t>
   </si>
   <si>
-    <t>In your file does not import into the system, review the erros messages and the notes.</t>
-  </si>
-  <si>
     <t>For this screenshot, the dates provided in the file were not the proper format.</t>
   </si>
   <si>
@@ -1414,25 +1413,797 @@
     <t>A sample template to understand what a import file looks like.</t>
   </si>
   <si>
-    <t>An explaination of fields used in JIRA.</t>
-  </si>
-  <si>
     <t>A sample of templates based on the Import Template</t>
   </si>
   <si>
     <t>A sample confirmation file that can be used to design a space's functionality repeatedly.</t>
   </si>
   <si>
-    <t>Sample of a sucessful and unsucessful import of a template.</t>
-  </si>
-  <si>
-    <t>A breakdown of how the confiuration file maps to JIRA and where to find key functions.</t>
-  </si>
-  <si>
     <t>A small step-by-step visual of uploading tasks to JIRA.</t>
   </si>
   <si>
     <t>A small reminded about using Notepad++ in review and editing of .CSV files.</t>
+  </si>
+  <si>
+    <t>Another example of mapping values.</t>
+  </si>
+  <si>
+    <t>If your file does not import into the system, review the errors messages and the notes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This screenshot shows that the .CSV file uploaded properly, but a commenter name could not be found in the </t>
+  </si>
+  <si>
+    <t>Also, the Component lead uploaded as null and was not found.</t>
+  </si>
+  <si>
+    <t>COMMENT (Mapped from the COMMENT BODY column in the .CSV file).</t>
+  </si>
+  <si>
+    <t>Developed by Shawn Latta to learn hands on to use a mass updating method for JIRA.</t>
+  </si>
+  <si>
+    <t>If you want to change the project lead, where in Project Settings do you do that?</t>
+  </si>
+  <si>
+    <t>Workflows</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>People</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>What happens if you select the + sign shown in the first of the three gray panels?</t>
+  </si>
+  <si>
+    <t>It will create a new board.</t>
+  </si>
+  <si>
+    <t>It will create a new project.</t>
+  </si>
+  <si>
+    <t>It will add an item.</t>
+  </si>
+  <si>
+    <t>It will create a new issue.</t>
+  </si>
+  <si>
+    <t>when the issue is late</t>
+  </si>
+  <si>
+    <t>issues are always reassigned when moved to review</t>
+  </si>
+  <si>
+    <t>when Patrice is an administrator</t>
+  </si>
+  <si>
+    <t>when a rule has been added</t>
+  </si>
+  <si>
+    <t>The issue that Max was assigned for his team's project is almost complete. What status should it have in the project's Kanban board?</t>
+  </si>
+  <si>
+    <t>In progress</t>
+  </si>
+  <si>
+    <t>Backlog</t>
+  </si>
+  <si>
+    <t>Selected for development</t>
+  </si>
+  <si>
+    <t>the status of an issue</t>
+  </si>
+  <si>
+    <t>the card layout</t>
+  </si>
+  <si>
+    <t>the card colors</t>
+  </si>
+  <si>
+    <t>the board configuration</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>Another issue needs to be finished before this one can be worked on.</t>
+  </si>
+  <si>
+    <t>The URL in the issue is not working.</t>
+  </si>
+  <si>
+    <t>The issue is linked to another project board.</t>
+  </si>
+  <si>
+    <t>The issue is in the backlog.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">When Patrice finishes an issue that was assigned to her and moves it from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In Progress</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> column to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Review </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>column, it's no longer assigned to Patrice. When would that happen?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In a Kanban board, a standard user has permissions to change </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9.6"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_____.</t>
+    </r>
+  </si>
+  <si>
+    <t>The administrator of a Kanban project clicked the Link issue button. What does that mean?</t>
+  </si>
+  <si>
+    <t>By default, who is assigned as the reporter for an issue in Kanban?</t>
+  </si>
+  <si>
+    <t>the assignee</t>
+  </si>
+  <si>
+    <t>the person who created the issue</t>
+  </si>
+  <si>
+    <t>it's unassigned by default</t>
+  </si>
+  <si>
+    <t>the person assigned to the issue before it</t>
+  </si>
+  <si>
+    <t>What is an effect of limiting the number of work in progress issues in a project?</t>
+  </si>
+  <si>
+    <t>It increases multitasking, which decreases efficiency.</t>
+  </si>
+  <si>
+    <t>The team misses tasks.</t>
+  </si>
+  <si>
+    <t>It creates work siloes, which disrupt teamwork.</t>
+  </si>
+  <si>
+    <t>The team finishes projects they have started, improving flow.</t>
+  </si>
+  <si>
+    <t>JIRA Cloud 1:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Review the image below. Why is the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Selected for Development </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>column yellow?</t>
+    </r>
+  </si>
+  <si>
+    <t>The issue in that column is high priority.</t>
+  </si>
+  <si>
+    <t>There are too many issues in that column.</t>
+  </si>
+  <si>
+    <t>There are not enough issues in that column.</t>
+  </si>
+  <si>
+    <t>The issues in that column are overdue.</t>
+  </si>
+  <si>
+    <t>Actually, there is only 1 issue in the column, which violates the work in progress limit of 2.</t>
+  </si>
+  <si>
+    <t>A cumulative flow diagram can be used to _____.</t>
+  </si>
+  <si>
+    <t>identify who was assigned to each issue in a workflow</t>
+  </si>
+  <si>
+    <t>see how long an individual step took on an issue</t>
+  </si>
+  <si>
+    <t>see how long issues were in each status of workflow</t>
+  </si>
+  <si>
+    <t>assess how many issues are in the backlog</t>
+  </si>
+  <si>
+    <t>JIRA Cloud 2:</t>
+  </si>
+  <si>
+    <t>What is the primary difference between lean and agile principles?</t>
+  </si>
+  <si>
+    <t>Lean principles aim to eliminate waste, while agile aims to respond to change.</t>
+  </si>
+  <si>
+    <t>Lean principles focus on processes, while agile focuses on tools.</t>
+  </si>
+  <si>
+    <t>Lean principles value customer collaboration, while agile values contract negotiation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jira Query Language (JQL) </t>
+  </si>
+  <si>
+    <t>sprint review</t>
+  </si>
+  <si>
+    <t>sprint backlog</t>
+  </si>
+  <si>
+    <t>product backlog</t>
+  </si>
+  <si>
+    <t>sprint goal</t>
+  </si>
+  <si>
+    <t>Hanai is leading a Scrum team meeting. She wants to improve sprint planning accuracy. Which artifact can help with this?</t>
+  </si>
+  <si>
+    <t>Isla, a project administrator, wants to ensure effective sprint execution in a new Scrum project. What is her next step after creating sprint backlogs?</t>
+  </si>
+  <si>
+    <t>Initiate sprint execution.</t>
+  </si>
+  <si>
+    <t>Review sprint reports.</t>
+  </si>
+  <si>
+    <t>Configure sprint goals.</t>
+  </si>
+  <si>
+    <t>If a Scrum Master wants to enhance team productivity during sprint planning, what should they prioritize?</t>
+  </si>
+  <si>
+    <t>defining sprint goals</t>
+  </si>
+  <si>
+    <t>setting sprint duration</t>
+  </si>
+  <si>
+    <t>refining the product backlog</t>
+  </si>
+  <si>
+    <t>In Jira, which feature facilitates the dissemination of filtered results among team members through electronic correspondence, ensuring real-time access to updated data?</t>
+  </si>
+  <si>
+    <t>collaborative search syndication</t>
+  </si>
+  <si>
+    <t>dynamic report dispatch</t>
+  </si>
+  <si>
+    <t>issue link distribution</t>
+  </si>
+  <si>
+    <t>agile board notification</t>
+  </si>
+  <si>
+    <t>John needs to swiftly pinpoint particular issues in a ticketing system. Which search method should he use for a text-based query?</t>
+  </si>
+  <si>
+    <t>natural language processing</t>
+  </si>
+  <si>
+    <t>regular expressions</t>
+  </si>
+  <si>
+    <t>XPath</t>
+  </si>
+  <si>
+    <t>JQL</t>
+  </si>
+  <si>
+    <t>Functionality</t>
+  </si>
+  <si>
+    <t>Command Word</t>
+  </si>
+  <si>
+    <t>PROJECT</t>
+  </si>
+  <si>
+    <t>ORDER BY</t>
+  </si>
+  <si>
+    <t>DESC</t>
+  </si>
+  <si>
+    <t>Notation that results need to be ordered.</t>
+  </si>
+  <si>
+    <t>Description of task within a project.</t>
+  </si>
+  <si>
+    <t>https://support.atlassian.com/jira-service-management-cloud/docs/use-advanced-search-with-jira-query-language-jql/</t>
+  </si>
+  <si>
+    <t>EMPTY</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
+    <t>AND</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>NOT (!=)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used to search for work items where a given field does not have a value. </t>
+  </si>
+  <si>
+    <t>Usage Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note that EMPTY can only be used with fields that support the IS and IS NOT operators. </t>
+  </si>
+  <si>
+    <t>Note that NULL can only be used with fields that support the IS and IS NOT operators.</t>
+  </si>
+  <si>
+    <t>Used when both items are wanted.</t>
+  </si>
+  <si>
+    <t>Used when at least 1 item is wanted.</t>
+  </si>
+  <si>
+    <t>JQL keywords</t>
+  </si>
+  <si>
+    <t>JQL operators</t>
+  </si>
+  <si>
+    <t>https://support.atlassian.com/jira-service-management-cloud/docs/jql-operators/</t>
+  </si>
+  <si>
+    <t>EQUALS (=)</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>GREATER THAN (&gt;)</t>
+  </si>
+  <si>
+    <t>LESS THAN (&lt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using "IN" is equivalent to using multiple EQUALS (=) statements, but is shorter and more convenient. </t>
+  </si>
+  <si>
+    <t>NOT IN</t>
+  </si>
+  <si>
+    <t>The "NOT IN" operator will not match a field that is empty/null.</t>
+  </si>
+  <si>
+    <t>CONTAINS (~)</t>
+  </si>
+  <si>
+    <t>When using the "~" operator, the value on the right-hand side of the operator can be specified using Jira text-search syntax.</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field is not one of multiple specified values.</t>
+  </si>
+  <si>
+    <t>DOES NOT CONTAIN (!~)</t>
+  </si>
+  <si>
+    <t>When using the "!~" operator, the value on the right-hand side of the operator can be specified using Jira text-search syntax.</t>
+  </si>
+  <si>
+    <t>IS</t>
+  </si>
+  <si>
+    <t>IS NOT</t>
+  </si>
+  <si>
+    <t>The "IS" operator can only be used with EMPTY or NULL.</t>
+  </si>
+  <si>
+    <t>Not all fields are compatible with this operator.</t>
+  </si>
+  <si>
+    <t>The "IS NOT" operator can only be used with EMPTY or NULL.</t>
+  </si>
+  <si>
+    <t>WAS</t>
+  </si>
+  <si>
+    <t>Used to combine multiple clauses.</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field exactly matches the specified search value.</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field is greater than the specified value.</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field is one of multiple specified values.</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field is lesser than the specified value.</t>
+  </si>
+  <si>
+    <t>Used to negate individual clauses; exclusion.</t>
+  </si>
+  <si>
+    <t>Name of the project that one is looking into.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used to search for work items where the value of the specified field matches the specified value. </t>
+  </si>
+  <si>
+    <t>used to search for work items where the value of the specified field is not a "fuzzy" match for the specified value.</t>
+  </si>
+  <si>
+    <t>Operator can only be used with fields that support ordering (e.g. date fields and version fields), and cannot be used with text fields.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Note: cannot be used with text fields; can be appended to the </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Than</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> functions.</t>
+    </r>
+  </si>
+  <si>
+    <t>Used to find work items that currently have or previously had the specified value for the specified field.</t>
+  </si>
+  <si>
+    <t>This operator can be used with the Assignee, Fix Version, Priority, Reporter, Resolution, and Status fields only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFTER </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEFORE </t>
+  </si>
+  <si>
+    <t>BY</t>
+  </si>
+  <si>
+    <t>DURING</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>After a certain date; not a standalone command.</t>
+  </si>
+  <si>
+    <t>Before a certain date; not a standalone command.</t>
+  </si>
+  <si>
+    <t>User; not a standalone command.</t>
+  </si>
+  <si>
+    <t>Date range; not a standalone command.</t>
+  </si>
+  <si>
+    <t>Exact date; not a standalone command.</t>
+  </si>
+  <si>
+    <t>Predicate of WAS.</t>
+  </si>
+  <si>
+    <t>WAS IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Using "IN" is equivalent to using multiple WAS statements, but is shorter and more convenient. </t>
+  </si>
+  <si>
+    <t>WAS NOT IN</t>
+  </si>
+  <si>
+    <t>Used to search for work items where the value of the specified field has never been one of multiple specified values.</t>
+  </si>
+  <si>
+    <t>WAS NOT</t>
+  </si>
+  <si>
+    <t>Used to find work items that have never had the specified value for the specified field.</t>
+  </si>
+  <si>
+    <t>CHANGED</t>
+  </si>
+  <si>
+    <t>Used to find work items that have a value that had changed for the specified field.</t>
+  </si>
+  <si>
+    <t>Predicate of CHANGE.</t>
+  </si>
+  <si>
+    <t>This operator can be used with the Assignee, Fix Version, Priority, Reporter, Resolution, and Status fields only. Predicates of WAS can be used as well.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FROM </t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+  <si>
+    <t>The "new" owner at the time the task was changed.</t>
+  </si>
+  <si>
+    <t>The "original" owner at the time the task was changed.</t>
+  </si>
+  <si>
+    <t>Your coworker aims to navigate Jira effectively for "A Project" using JQL queries, but they need aid with autocomplete and functions. Which feature can help them simplify JQL query creation?</t>
+  </si>
+  <si>
+    <t>the query builder</t>
+  </si>
+  <si>
+    <t>the JQL helper plug-in</t>
+  </si>
+  <si>
+    <t>the Jira query wizard</t>
+  </si>
+  <si>
+    <t>the JQL query library</t>
+  </si>
+  <si>
+    <t>Your project manager seeks to simplify Jira queries for your team. Which feature helps your team to avoid hard-coded values in search clauses?</t>
+  </si>
+  <si>
+    <t>autocomplete</t>
+  </si>
+  <si>
+    <t>advanced filters</t>
+  </si>
+  <si>
+    <t>functions</t>
+  </si>
+  <si>
+    <t>Keywords for JIRA Query Language.</t>
+  </si>
+  <si>
+    <t>Sample of a successful and unsuccessful import of a template.</t>
+  </si>
+  <si>
+    <t>A breakdown of how the configuration file maps to JIRA and where to find key functions.</t>
+  </si>
+  <si>
+    <t>An explanation of fields used in JIRA.</t>
+  </si>
+  <si>
+    <t>JIRA Cloud 3:</t>
+  </si>
+  <si>
+    <t>George wants to create a filter that shows only the issues assigned to him that are currently in progress. How should he proceed?</t>
+  </si>
+  <si>
+    <t>Create a JQL query with status = "In Progress" AND assignee = Userpresent().</t>
+  </si>
+  <si>
+    <t>Create a JQL query with status = "Open" AND assignee = currentUser().</t>
+  </si>
+  <si>
+    <t>Create a JQL query with status = "In Progress" AND assignee = currentUser().</t>
+  </si>
+  <si>
+    <t>Halinka needs to ensure that her team sees only issues related to multiple projects on their board. How can she achieve this using board filters?</t>
+  </si>
+  <si>
+    <t>Create a quick filter that includes issues from all desired projects.</t>
+  </si>
+  <si>
+    <t>Use the New Subscription link to add multiple projects to the board filter.</t>
+  </si>
+  <si>
+    <t>Use the Edit Permissions link in the filter details to include multiple projects.</t>
+  </si>
+  <si>
+    <t>Assign the board filter to a query including issues from multiple project keys.</t>
+  </si>
+  <si>
+    <t>What is the purpose of using quick filters in Board settings?</t>
+  </si>
+  <si>
+    <t>to limit the visibility of issues on the board based on tags</t>
+  </si>
+  <si>
+    <t>to limit the visibility of issues on the board based on specific criteria</t>
+  </si>
+  <si>
+    <t>to filter issues by their priority levels</t>
+  </si>
+  <si>
+    <t>What is the purpose of using epics in project management within Jira?</t>
+  </si>
+  <si>
+    <t>to categorize tasks based on their priority levels</t>
+  </si>
+  <si>
+    <t>to ensure that only bugs and defects are tracked in the project</t>
+  </si>
+  <si>
+    <t>to organize large work items that span multiple iterations or projects</t>
+  </si>
+  <si>
+    <t>to represent small, individual tasks that can be completed quickly</t>
+  </si>
+  <si>
+    <t>Taphanes wants to manage and visualize her project's large work items using the Roadmap feature. What should she do first to begin using this feature?</t>
+  </si>
+  <si>
+    <t>Use the Epic Link field to enable the Roadmap feature.</t>
+  </si>
+  <si>
+    <t>Create a new Kanban board with the Roadmap enabled.</t>
+  </si>
+  <si>
+    <t>Go to Board settings and enable the Roadmap feature.</t>
+  </si>
+  <si>
+    <t>Click on the Global Search field and select Roadmap.</t>
+  </si>
+  <si>
+    <t>Shane needs to organize and manage his team's work items in a Kanban project using a visual planning tool. What is his first step to start utilizing this feature?</t>
+  </si>
+  <si>
+    <t>Use the Epic Link field to view the roadmap.</t>
+  </si>
+  <si>
+    <t>Turn off the Backlog feature in Project settings.</t>
+  </si>
+  <si>
+    <t>Select Roadmap in the sidebar to view the project roadmap.</t>
+  </si>
+  <si>
+    <t>Create a new project with Roadmap enabled.</t>
+  </si>
+  <si>
+    <t>Why are dashboards valuable tools for teams in project management?</t>
+  </si>
+  <si>
+    <t>They focus on project progress.</t>
+  </si>
+  <si>
+    <t>They offer a configurable view of project work.</t>
+  </si>
+  <si>
+    <t>They provide a platform for personal task organization.</t>
+  </si>
+  <si>
+    <t>Avilius wants to showcase project progress to his team using dashboards. How can he customize his dashboard to display a sprint effectively?</t>
+  </si>
+  <si>
+    <t>by configuring Sprint Project Gadget</t>
+  </si>
+  <si>
+    <t>by configuring Sprint Health Gadget</t>
+  </si>
+  <si>
+    <t>by selecting Activity Sprint Gadget</t>
+  </si>
+  <si>
+    <t>by selecting Start sprint</t>
+  </si>
+  <si>
+    <t>How does understanding agile principles and the Jira family help in effective project management?</t>
+  </si>
+  <si>
+    <t>by going through continuous improvement using Jira</t>
+  </si>
+  <si>
+    <t>by using fixed methodologies in Jira</t>
+  </si>
+  <si>
+    <t>by customizing tools like Jira</t>
+  </si>
+  <si>
+    <t>As a Jira administrator, Julija wants to set a work in progress limit for the Build column in a Kanban project. What should she do first?</t>
+  </si>
+  <si>
+    <t>Go to Board settings &gt; Columns, and then create a new column named Build with the desired limit.</t>
+  </si>
+  <si>
+    <t>Go to Board settings &gt; Columns, and then set the maximum limit to two for the Build column.</t>
+  </si>
+  <si>
+    <t>Go to Board settings &gt; Swimlanes, and then configure the work in progress limit for the Build column.</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +2213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1572,6 +2343,63 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Webdings"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.6"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Webdings"/>
+      <family val="1"/>
+      <charset val="2"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -1648,7 +2476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1741,9 +2569,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1754,11 +2579,11 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1770,8 +2595,45 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1781,8 +2643,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDDDDFF"/>
       <color rgb="FFFFFFCC"/>
-      <color rgb="FFDDDDFF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -2154,14 +3016,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>242</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>212</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>342171</xdr:colOff>
-      <xdr:row>286</xdr:row>
-      <xdr:rowOff>130423</xdr:rowOff>
+      <xdr:row>256</xdr:row>
+      <xdr:rowOff>143758</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2184,8 +3046,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="44622720"/>
-          <a:ext cx="5828571" cy="8171428"/>
+          <a:off x="0" y="38616255"/>
+          <a:ext cx="5828571" cy="8095228"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2198,14 +3060,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>289</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>256</xdr:row>
+      <xdr:rowOff>43815</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>477258</xdr:colOff>
-      <xdr:row>309</xdr:row>
-      <xdr:rowOff>20497</xdr:rowOff>
+      <xdr:row>276</xdr:row>
+      <xdr:rowOff>64312</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2228,8 +3090,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="53218080"/>
-          <a:ext cx="7171428" cy="3666667"/>
+          <a:off x="0" y="46611540"/>
+          <a:ext cx="7182858" cy="3639997"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2779,6 +3641,133 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>139277</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="a screenshot of a Jira Kanban project with PROJ board at the top, three grey boxes labeled to do, in progress, and done from left to right, and a grey button with a plus sign">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{83112F22-6EE1-DC5E-756C-25B14389305F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1729740"/>
+          <a:ext cx="6235277" cy="3169920"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>227557</xdr:colOff>
+      <xdr:row>96</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2" descr="a screenshot of a Kanban board with four grey columns, and one column labeled selected for development is yellow ">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF841EE2-7B97-CAF1-5DAF-E9AB89C49FE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="14241780"/>
+          <a:ext cx="7542757" cy="4130040"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3096,209 +4085,2255 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7ADE341-5C97-4646-93AF-E884507450A9}">
-  <dimension ref="C5:G20"/>
+  <dimension ref="C5:O18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:7" s="55" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" s="54" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C9" s="59" t="s">
+    <row r="5" spans="3:15" s="54" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="C5" s="53" t="s">
+        <v>330</v>
+      </c>
+      <c r="O5" s="59" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C9" s="13" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C10" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C11" s="49" t="s">
+        <v>428</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C12" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="D9" s="59"/>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C10" s="59"/>
-      <c r="D10" s="59"/>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C11" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="59"/>
-      <c r="F11" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G11" s="13" t="s">
+    </row>
+    <row r="13" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C13" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="F13" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G13" s="13" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C12" s="60" t="s">
-        <v>333</v>
-      </c>
-      <c r="D12" s="59"/>
-      <c r="F12" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G12" s="13" t="s">
+    <row r="14" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C14" s="58" t="s">
+        <v>334</v>
+      </c>
+      <c r="F14" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C15" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="F15" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C13" s="60" t="s">
-        <v>334</v>
-      </c>
-      <c r="D13" s="59"/>
-      <c r="F13" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C14" s="60" t="s">
+    <row r="16" spans="3:15" x14ac:dyDescent="0.3">
+      <c r="C16" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="F16" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="F14" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C15" s="60" t="s">
+      <c r="G16" s="13" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C17" s="58" t="s">
+        <v>313</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C18" s="58" t="s">
         <v>318</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="F15" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G15" s="13" t="s">
+      <c r="F18" s="57" t="s">
+        <v>335</v>
+      </c>
+      <c r="G18" s="13" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C16" s="60" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" s="59"/>
-      <c r="F16" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C17" s="60" t="s">
-        <v>314</v>
-      </c>
-      <c r="D17" s="59"/>
-      <c r="F17" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C18" s="60" t="s">
-        <v>319</v>
-      </c>
-      <c r="D18" s="59"/>
-      <c r="F18" s="58" t="s">
-        <v>336</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C11" location="'JIRA Import Template'!A1" display="JIRA Import Template" xr:uid="{81F83669-D722-426A-8AC8-58765989B644}"/>
-    <hyperlink ref="C12" location="'JIRA Fields'!A1" display="JIRA Fields" xr:uid="{A832CDA5-3428-4EEF-845A-139C7769E391}"/>
+    <hyperlink ref="C12" location="'JIRA Import Template'!A1" display="JIRA Import Template" xr:uid="{81F83669-D722-426A-8AC8-58765989B644}"/>
     <hyperlink ref="C13" location="'Sample .csv'!A1" display="Sample.csv" xr:uid="{107B5426-FAB5-4853-80B6-C9731FCFAE26}"/>
     <hyperlink ref="C14" location="'How to upload a Space to JIRA'!A1" display="How to upload a Space to JIRA" xr:uid="{35489D90-CBFA-46F5-9EBB-36F4205E0F97}"/>
     <hyperlink ref="C18" location="'Using Notepad Plus'!A1" display="Using Notepad Plus" xr:uid="{08A79443-7C3B-4B4E-A2B6-DFA025FEA2CF}"/>
     <hyperlink ref="C17" location="'Upload to Data Mapping'!A1" display="Upload to Data Mapping" xr:uid="{FA9354BA-12AC-48A8-8441-EE3990C08D3B}"/>
     <hyperlink ref="C16" location="'Sample Import Log'!A1" display="Sample Import Log" xr:uid="{87156EB9-BDFB-4BD0-80D3-4E69B92C37B7}"/>
     <hyperlink ref="C15" location="'Sample Configuration File'!A1" display="Sample Configuration File" xr:uid="{8EE6442E-AB8B-4B2C-B2BD-27108394142C}"/>
+    <hyperlink ref="C10" location="'JIRA Fields'!A1" display="JIRA Fields" xr:uid="{530E024A-BC92-4B3C-BE4A-5C326AEDA244}"/>
+    <hyperlink ref="C11" location="JQL!A1" display="JQL" xr:uid="{17DD55A0-D129-463C-907C-B366C84E7329}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BBCBC4-F056-4E6C-ACB7-1B5DC3A576B9}">
+  <dimension ref="A1:AA130"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="21" max="21" width="24.21875" customWidth="1"/>
+    <col min="22" max="22" width="25.77734375" style="36" customWidth="1"/>
+    <col min="23" max="23" width="23.77734375" style="36" customWidth="1"/>
+    <col min="24" max="25" width="34.44140625" customWidth="1"/>
+    <col min="26" max="26" width="74.5546875" customWidth="1"/>
+    <col min="27" max="27" width="16.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" s="44" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="45" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="U2" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="V2" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="W2" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="X2" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="Y2" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z2" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA2" s="26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U3" t="s">
+        <v>0</v>
+      </c>
+      <c r="V3" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="W3" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" t="s">
+        <v>159</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U4" t="s">
+        <v>79</v>
+      </c>
+      <c r="V4" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="W4" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="X4" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="W5" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="X5" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z5" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U6" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="X6" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U7" t="s">
+        <v>1</v>
+      </c>
+      <c r="V7" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="W7" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="X7" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>178</v>
+      </c>
+      <c r="Z7" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U8" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="V8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="W8" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="X8" s="38"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U9" s="50" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="51">
+        <v>1</v>
+      </c>
+      <c r="W9" s="51">
+        <v>2</v>
+      </c>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="52"/>
+      <c r="Z9" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U10" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="W10" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X10" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z10" s="29" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U11" t="s">
+        <v>5</v>
+      </c>
+      <c r="V11" s="36">
+        <v>1</v>
+      </c>
+      <c r="W11" s="36">
+        <v>2</v>
+      </c>
+      <c r="X11" t="s">
+        <v>169</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>182</v>
+      </c>
+      <c r="Z11" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U12" t="s">
+        <v>11</v>
+      </c>
+      <c r="V12" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="W12" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="X12" t="s">
+        <v>167</v>
+      </c>
+      <c r="Z12" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U13" t="s">
+        <v>12</v>
+      </c>
+      <c r="V13" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="W13" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="X13" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U14" t="s">
+        <v>21</v>
+      </c>
+      <c r="V14" s="34">
+        <v>46112</v>
+      </c>
+      <c r="W14" s="34">
+        <v>46113</v>
+      </c>
+      <c r="X14" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>180</v>
+      </c>
+      <c r="Z14" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U15" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="V15" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="W15" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="52"/>
+      <c r="Z15" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="U16" t="s">
+        <v>26</v>
+      </c>
+      <c r="V16" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="W16" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="X16" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>181</v>
+      </c>
+      <c r="Z16" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="U17" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="V17" s="51"/>
+      <c r="W17" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17" s="50"/>
+      <c r="Y17" s="52"/>
+      <c r="Z17" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="U18" t="s">
+        <v>17</v>
+      </c>
+      <c r="V18" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="W18" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="X18" t="s">
+        <v>173</v>
+      </c>
+      <c r="Z18" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z19" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z20" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z21" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z22" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z23" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z24" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z25" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z26" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z27" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z28" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="AA28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z29" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z30" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z31" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="21:27" x14ac:dyDescent="0.3">
+      <c r="Z32" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z33" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z34" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z35" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z36" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z37" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z38" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="AA38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z39" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA39">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z40" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z41" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z42" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z43" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z44" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA44">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z45" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z46" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z47" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z48" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z49" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z50" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA50">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z51" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z52" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z53" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z54" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z55" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA55">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z56" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z57" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z58" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z59" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA59">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z60" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z61" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z62" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z63" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="AA63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z64" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA64">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z65" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z66" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="AA66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z67" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z68" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="AA68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z69" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z70" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z71" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="AA71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z72" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z73" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z74" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z75" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z76" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="AA76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z77" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z78" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z79" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z80" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA80">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z81" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z82" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z83" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="AA83">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z84" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA84">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z85" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z86" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z87" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="AA87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z88" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z89" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z90" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA90">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z91" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="AA91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z92" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z93" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z94" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA94">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z95" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z96" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z97" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z98" s="32" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA98">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z99" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z100" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z101" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z102" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z103" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z104" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z105" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="AA105">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z106" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z107" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z108" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z109" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z110" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z111" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z112" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA112">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z113" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z114" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA114">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z115" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z116" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z117" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z118" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z119" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z120" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z121" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z122" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z123" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="AA123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z124" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z125" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="AA125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z126" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z127" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="AA127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z128" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z129" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA129">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" spans="26:27" x14ac:dyDescent="0.3">
+      <c r="Z130" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA130">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="U2:AA129" xr:uid="{80BBCBC4-F056-4E6C-ACB7-1B5DC3A576B9}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82F7BD1E-95D1-43CD-B496-F77502201342}">
   <dimension ref="A1:N79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
-        <v>319</v>
+    <row r="1" spans="1:14" s="44" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="45" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="N14" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="43" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N43" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N44" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N47" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="76" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N76" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="77" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N77" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="79" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N79" t="s">
-        <v>330</v>
+        <v>329</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E8902D4-7A27-4DFD-A14A-334F5DDB1853}">
+  <dimension ref="A1:B214"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="45" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="61" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="61" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B31" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B32" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="61" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B39" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="61" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B43" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B46" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="61" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="60" t="s">
+        <v>370</v>
+      </c>
+      <c r="B49" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="61" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A55" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B55" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" s="25" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B61" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A62" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B62" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="25" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B70" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A100" s="25"/>
+      <c r="B100" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A101" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B101" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A104" s="25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B106" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A107" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B107" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B108" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A111" s="45" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="25" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A114" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B114" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B115" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B116" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="25" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B119" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A120" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B120" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B121" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B122" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A124" s="25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A125" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B125" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B126" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B127" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="25" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B130" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B131" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A132" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B132" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A134" s="25" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A135" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B135" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B136" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B137" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B138" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="25" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B141" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B142" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B143" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A144" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B144" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="25" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B147" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A148" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B148" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B149" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B150" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="25" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B153" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B154" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A155" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B155" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A158" s="45" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="25" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B161" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B162" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A163" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B163" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A166" s="25" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B167" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B168" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B169" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A170" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B170" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A172" s="25" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B173" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A174" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B174" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B175" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" spans="1:2" s="25" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A177" s="25" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B178" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B179" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A180" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B180" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B181" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="25" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B184" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B185" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A186" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B186" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B187" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A189" s="25" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B190" s="74" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B191" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A192" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B192" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B193" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="25" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B196" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B197" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B198" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" s="25" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="25" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B201" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A202" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B202" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B203" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B204" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A206" s="25" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B207" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B208" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A209" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B209" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A211" s="25" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B212" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A213" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="B213" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B214" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -3308,270 +6343,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB44B18F-50F4-4DFC-BC16-755E6782D836}">
-  <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" customWidth="1"/>
-    <col min="5" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.33203125" customWidth="1"/>
-    <col min="11" max="11" width="24.77734375" customWidth="1"/>
-    <col min="12" max="12" width="13.33203125" customWidth="1"/>
-    <col min="13" max="13" width="27.33203125" customWidth="1"/>
-    <col min="14" max="14" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" s="3" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>186</v>
-      </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-    </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="56" t="s">
-        <v>332</v>
-      </c>
-      <c r="O2" s="5"/>
-    </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="10">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="10">
-        <v>1</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4" s="24">
-        <v>46112</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="10">
-        <v>2</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="I5" s="10">
-        <v>2</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="L5" s="24">
-        <v>46113</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="F1:J1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{E466F571-DA4C-4BB2-A340-D206A003CE51}"/>
-    <hyperlink ref="F4" r:id="rId2" xr:uid="{BC5CA502-2574-429E-B85B-368A77BFF577}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{D7CCAB5A-37F9-492C-93C8-2F960577DD41}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{63034A3B-86A0-4370-B0D7-887717624BC3}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8E2B1336-90CA-4133-9E13-AE1AF7283763}">
-          <x14:formula1>
-            <xm:f>'Drop Downs'!$C$1:$D$1</xm:f>
-          </x14:formula1>
-          <xm:sqref>D4</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88095DBA-DCB4-4CD7-9AC8-6329752DD4E2}">
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D2AFE65-E5D5-44A8-983D-EB396FF1A9A4}">
   <dimension ref="A1:N163"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3928,7 +6699,641 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6095147-C3C8-4A68-B8C7-EF2FD7B98EF3}">
+  <dimension ref="A1:K34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.88671875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="54.33203125" style="8" customWidth="1"/>
+    <col min="3" max="3" width="42.5546875" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="70" t="s">
+        <v>405</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="71" t="s">
+        <v>430</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>429</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="72" t="s">
+        <v>482</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>487</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="67" t="s">
+        <v>439</v>
+      </c>
+      <c r="B4" s="68" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4" s="68" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="72" t="s">
+        <v>483</v>
+      </c>
+      <c r="B5" s="64" t="s">
+        <v>488</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="73" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="68" t="s">
+        <v>489</v>
+      </c>
+      <c r="C6" s="68" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="72" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="64" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="64" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="67" t="s">
+        <v>458</v>
+      </c>
+      <c r="B8" s="68" t="s">
+        <v>476</v>
+      </c>
+      <c r="C8" s="68" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="66" t="s">
+        <v>433</v>
+      </c>
+      <c r="B9" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="C9" s="64"/>
+    </row>
+    <row r="10" spans="1:11" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="67" t="s">
+        <v>461</v>
+      </c>
+      <c r="B10" s="68" t="s">
+        <v>477</v>
+      </c>
+      <c r="C10" s="68" t="s">
+        <v>462</v>
+      </c>
+      <c r="K10" s="69"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="72" t="s">
+        <v>485</v>
+      </c>
+      <c r="B11" s="64" t="s">
+        <v>490</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="67" t="s">
+        <v>437</v>
+      </c>
+      <c r="B12" s="68" t="s">
+        <v>442</v>
+      </c>
+      <c r="C12" s="68" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="66" t="s">
+        <v>451</v>
+      </c>
+      <c r="B13" s="64" t="s">
+        <v>470</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="73" t="s">
+        <v>503</v>
+      </c>
+      <c r="B14" s="68" t="s">
+        <v>506</v>
+      </c>
+      <c r="C14" s="68" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="66" t="s">
+        <v>453</v>
+      </c>
+      <c r="B15" s="64" t="s">
+        <v>471</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="67" t="s">
+        <v>452</v>
+      </c>
+      <c r="B16" s="68" t="s">
+        <v>472</v>
+      </c>
+      <c r="C16" s="68" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="66" t="s">
+        <v>463</v>
+      </c>
+      <c r="B17" s="64" t="s">
+        <v>465</v>
+      </c>
+      <c r="C17" s="64" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="67" t="s">
+        <v>464</v>
+      </c>
+      <c r="B18" s="68" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" s="68" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="66" t="s">
+        <v>454</v>
+      </c>
+      <c r="B19" s="64" t="s">
+        <v>473</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="67" t="s">
+        <v>441</v>
+      </c>
+      <c r="B20" s="68" t="s">
+        <v>474</v>
+      </c>
+      <c r="C20" s="68"/>
+    </row>
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="66" t="s">
+        <v>456</v>
+      </c>
+      <c r="B21" s="64" t="s">
+        <v>460</v>
+      </c>
+      <c r="C21" s="64" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="67" t="s">
+        <v>438</v>
+      </c>
+      <c r="B22" s="68" t="s">
+        <v>442</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="72" t="s">
+        <v>486</v>
+      </c>
+      <c r="B23" s="64" t="s">
+        <v>491</v>
+      </c>
+      <c r="C23" s="64" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="67" t="s">
+        <v>440</v>
+      </c>
+      <c r="B24" s="68" t="s">
+        <v>469</v>
+      </c>
+      <c r="C24" s="68" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="66" t="s">
+        <v>432</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>434</v>
+      </c>
+      <c r="C25" s="64"/>
+    </row>
+    <row r="26" spans="1:3" s="15" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="67" t="s">
+        <v>431</v>
+      </c>
+      <c r="B26" s="68" t="s">
+        <v>475</v>
+      </c>
+      <c r="C26" s="68"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="66" t="s">
+        <v>504</v>
+      </c>
+      <c r="B27" s="64" t="s">
+        <v>505</v>
+      </c>
+      <c r="C27" s="64" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" s="15" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="67" t="s">
+        <v>468</v>
+      </c>
+      <c r="B28" s="68" t="s">
+        <v>480</v>
+      </c>
+      <c r="C28" s="68" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="66" t="s">
+        <v>493</v>
+      </c>
+      <c r="B29" s="64" t="s">
+        <v>472</v>
+      </c>
+      <c r="C29" s="64" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="15" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="67" t="s">
+        <v>497</v>
+      </c>
+      <c r="B30" s="68" t="s">
+        <v>498</v>
+      </c>
+      <c r="C30" s="68"/>
+    </row>
+    <row r="31" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="66" t="s">
+        <v>495</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>496</v>
+      </c>
+      <c r="C31" s="64" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="64"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+    </row>
+    <row r="33" spans="1:3" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="71" t="s">
+        <v>448</v>
+      </c>
+      <c r="B33" s="71" t="s">
+        <v>436</v>
+      </c>
+      <c r="C33" s="71"/>
+    </row>
+    <row r="34" spans="1:3" s="63" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="71" t="s">
+        <v>449</v>
+      </c>
+      <c r="B34" s="71" t="s">
+        <v>450</v>
+      </c>
+      <c r="C34" s="71"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:C31">
+    <sortCondition ref="A3:A31"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB44B18F-50F4-4DFC-BC16-755E6782D836}">
+  <dimension ref="A1:O5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.33203125" customWidth="1"/>
+    <col min="11" max="11" width="24.77734375" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" customWidth="1"/>
+    <col min="14" max="14" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" s="3" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+    </row>
+    <row r="2" spans="1:15" s="2" customFormat="1" ht="89.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="55" t="s">
+        <v>331</v>
+      </c>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" s="8" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="10">
+        <v>1</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="24">
+        <v>46112</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" s="8" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="10">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="10">
+        <v>2</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" s="24">
+        <v>46113</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="F1:J1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{E466F571-DA4C-4BB2-A340-D206A003CE51}"/>
+    <hyperlink ref="F4" r:id="rId2" xr:uid="{BC5CA502-2574-429E-B85B-368A77BFF577}"/>
+    <hyperlink ref="E5" r:id="rId3" xr:uid="{D7CCAB5A-37F9-492C-93C8-2F960577DD41}"/>
+    <hyperlink ref="F5" r:id="rId4" xr:uid="{63034A3B-86A0-4370-B0D7-887717624BC3}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8E2B1336-90CA-4133-9E13-AE1AF7283763}">
+          <x14:formula1>
+            <xm:f>'Drop Downs'!$C$1:$D$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>D4</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88095DBA-DCB4-4CD7-9AC8-6329752DD4E2}">
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D114742-F409-4389-A3D4-2FDA7E058BB6}">
   <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3952,7 +7357,7 @@
   <sheetData>
     <row r="1" spans="1:16" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F1" s="40"/>
       <c r="G1" s="40"/>
@@ -4315,9 +7720,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519A6580-B19C-4DA7-9801-52A84F66F38C}">
-  <dimension ref="A1:O193"/>
+  <dimension ref="A1:O259"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" s="3" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -4404,7 +7809,7 @@
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="L93" s="43" t="s">
+      <c r="L93" s="42" t="s">
         <v>219</v>
       </c>
     </row>
@@ -4419,7 +7824,7 @@
       </c>
     </row>
     <row r="104" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L104" s="44" t="s">
+      <c r="L104" s="43" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4429,7 +7834,7 @@
       </c>
     </row>
     <row r="106" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L106" s="44" t="s">
+      <c r="L106" s="43" t="s">
         <v>84</v>
       </c>
     </row>
@@ -4439,7 +7844,7 @@
       </c>
     </row>
     <row r="108" spans="12:12" x14ac:dyDescent="0.3">
-      <c r="L108" s="44"/>
+      <c r="L108" s="43"/>
     </row>
     <row r="109" spans="12:12" x14ac:dyDescent="0.3">
       <c r="L109" s="29"/>
@@ -4461,12 +7866,32 @@
     </row>
     <row r="191" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N191" t="s">
-        <v>227</v>
+        <v>343</v>
       </c>
     </row>
     <row r="193" spans="14:14" x14ac:dyDescent="0.3">
       <c r="N193" t="s">
-        <v>228</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="194" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N194" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="214" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N214" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="258" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N258" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="259" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N259" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -4479,7 +7904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0B2A75-0086-44D2-A1C2-C6EF5BB538BA}">
   <dimension ref="A1:K127"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4487,9 +7912,9 @@
     <col min="1" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
-        <v>318</v>
+    <row r="1" spans="1:11" s="44" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="45" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -4512,15 +7937,15 @@
         <v>92</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C7" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="K7" s="50" t="s">
-        <v>316</v>
+      <c r="K7" s="49" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4535,7 +7960,7 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="C10" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -4840,7 +8265,7 @@
     </row>
     <row r="71" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C71" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="72" spans="3:3" x14ac:dyDescent="0.3">
@@ -4850,7 +8275,7 @@
     </row>
     <row r="73" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C73" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="74" spans="3:3" x14ac:dyDescent="0.3">
@@ -5065,7 +8490,7 @@
     </row>
     <row r="116" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C116" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="117" spans="3:3" x14ac:dyDescent="0.3">
@@ -5075,7 +8500,7 @@
     </row>
     <row r="118" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C118" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="119" spans="3:3" x14ac:dyDescent="0.3">
@@ -5110,7 +8535,7 @@
     </row>
     <row r="125" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C125" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="126" spans="3:3" x14ac:dyDescent="0.3">
@@ -5131,7 +8556,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7735922-DA65-4A1A-8FD3-1873FF466D1E}">
   <dimension ref="A1:AD56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5141,1809 +8566,527 @@
     <col min="12" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
-        <v>278</v>
+    <row r="1" spans="1:19" s="44" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="A1" s="45" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B2" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="S2" s="26" t="s">
         <v>233</v>
-      </c>
-      <c r="S2" s="26" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B3" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B4" s="47" t="s">
         <v>279</v>
       </c>
-      <c r="S3" s="13" t="s">
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="46"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="46"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="46"/>
+      <c r="S4" s="13" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B4" s="48" t="s">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="B5" s="47" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="47"/>
-      <c r="K4" s="47"/>
-      <c r="L4" s="47"/>
-      <c r="M4" s="47"/>
-      <c r="N4" s="47"/>
-      <c r="O4" s="47"/>
-      <c r="P4" s="47"/>
-      <c r="Q4" s="47"/>
-      <c r="S4" s="13" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="46"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="46"/>
+      <c r="N5" s="46"/>
+      <c r="O5" s="46"/>
+      <c r="P5" s="46"/>
+      <c r="Q5" s="46"/>
+      <c r="S5" s="13" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B5" s="48" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="48"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="S5" s="13" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B6" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S6" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S7" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="S8" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B10" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="S10" s="13" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B11" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B12" s="13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="S12" s="13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B13" s="13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="S13" s="13" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="S14" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B15" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="S15" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B16" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="S16" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S17" s="13" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="S18" s="13" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="S19" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B20" s="13" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="S20" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="S21" s="13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B22" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="S22" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S23" s="13" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B24" s="13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="S24" s="13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B25" s="13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="S25" s="13" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B26" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S26" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B27" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="S27" s="13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B28" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="S28" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B29" s="13" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="S29" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B30" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="S30" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B31" s="47" t="s">
         <v>301</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="47"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="46"/>
+      <c r="N31" s="46"/>
+      <c r="O31" s="46"/>
+      <c r="P31" s="46"/>
+      <c r="Q31" s="46"/>
+      <c r="S31" s="13" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="31" spans="2:19" x14ac:dyDescent="0.3">
-      <c r="B31" s="48" t="s">
-        <v>302</v>
-      </c>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
-      <c r="H31" s="48"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="47"/>
-      <c r="S31" s="13" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="32" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B32" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="S32" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.3">
+      <c r="B33" s="47" t="s">
         <v>303</v>
       </c>
-      <c r="S32" s="13" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B33" s="48" t="s">
-        <v>304</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="48"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="48"/>
-      <c r="J33" s="47"/>
-      <c r="K33" s="47"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
-      <c r="O33" s="47"/>
-      <c r="P33" s="47"/>
-      <c r="Q33" s="47"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="47"/>
+      <c r="H33" s="47"/>
+      <c r="I33" s="47"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="46"/>
+      <c r="L33" s="46"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="46"/>
+      <c r="Q33" s="46"/>
       <c r="S33" s="13" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B34" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S34" s="13" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="35" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B35" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="S35" s="48" t="s">
-        <v>260</v>
-      </c>
-      <c r="T35" s="48"/>
-      <c r="U35" s="48"/>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="48"/>
-      <c r="Y35" s="48"/>
-      <c r="Z35" s="48"/>
-      <c r="AA35" s="48"/>
-      <c r="AB35" s="48"/>
-      <c r="AC35" s="48"/>
-      <c r="AD35" s="48"/>
+        <v>305</v>
+      </c>
+      <c r="S35" s="47" t="s">
+        <v>259</v>
+      </c>
+      <c r="T35" s="47"/>
+      <c r="U35" s="47"/>
+      <c r="V35" s="47"/>
+      <c r="W35" s="47"/>
+      <c r="X35" s="47"/>
+      <c r="Y35" s="47"/>
+      <c r="Z35" s="47"/>
+      <c r="AA35" s="47"/>
+      <c r="AB35" s="47"/>
+      <c r="AC35" s="47"/>
+      <c r="AD35" s="47"/>
     </row>
     <row r="36" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B36" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="S36" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B37" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="S37" s="48" t="s">
-        <v>262</v>
-      </c>
-      <c r="T37" s="48"/>
-      <c r="U37" s="48"/>
-      <c r="V37" s="48"/>
-      <c r="W37" s="48"/>
-      <c r="X37" s="48"/>
-      <c r="Y37" s="48"/>
-      <c r="Z37" s="48"/>
-      <c r="AA37" s="48"/>
-      <c r="AB37" s="48"/>
-      <c r="AC37" s="48"/>
-      <c r="AD37" s="48"/>
+        <v>306</v>
+      </c>
+      <c r="S37" s="47" t="s">
+        <v>261</v>
+      </c>
+      <c r="T37" s="47"/>
+      <c r="U37" s="47"/>
+      <c r="V37" s="47"/>
+      <c r="W37" s="47"/>
+      <c r="X37" s="47"/>
+      <c r="Y37" s="47"/>
+      <c r="Z37" s="47"/>
+      <c r="AA37" s="47"/>
+      <c r="AB37" s="47"/>
+      <c r="AC37" s="47"/>
+      <c r="AD37" s="47"/>
     </row>
     <row r="38" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B38" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="S38" s="49" t="s">
-        <v>263</v>
-      </c>
-      <c r="T38" s="49"/>
-      <c r="U38" s="49"/>
-      <c r="V38" s="49"/>
-      <c r="W38" s="49"/>
-      <c r="X38" s="49"/>
-      <c r="Y38" s="49"/>
-      <c r="Z38" s="49"/>
-      <c r="AA38" s="49"/>
-      <c r="AB38" s="49"/>
-      <c r="AC38" s="49"/>
-      <c r="AD38" s="49"/>
+        <v>307</v>
+      </c>
+      <c r="S38" s="48" t="s">
+        <v>262</v>
+      </c>
+      <c r="T38" s="48"/>
+      <c r="U38" s="48"/>
+      <c r="V38" s="48"/>
+      <c r="W38" s="48"/>
+      <c r="X38" s="48"/>
+      <c r="Y38" s="48"/>
+      <c r="Z38" s="48"/>
+      <c r="AA38" s="48"/>
+      <c r="AB38" s="48"/>
+      <c r="AC38" s="48"/>
+      <c r="AD38" s="48"/>
     </row>
     <row r="39" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B39" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="S39" s="13" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="40" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B40" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S40" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="41" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B41" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S41" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B42" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S42" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B43" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="S43" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="44" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B44" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="S44" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45" spans="2:30" x14ac:dyDescent="0.3">
-      <c r="B45" s="48" t="s">
-        <v>313</v>
-      </c>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="47"/>
-      <c r="Q45" s="47"/>
+      <c r="B45" s="47" t="s">
+        <v>312</v>
+      </c>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="46"/>
+      <c r="G45" s="46"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="46"/>
+      <c r="L45" s="46"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="46"/>
+      <c r="Q45" s="46"/>
       <c r="S45" s="13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="46" spans="2:30" x14ac:dyDescent="0.3">
       <c r="S46" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="47" spans="2:30" x14ac:dyDescent="0.3">
       <c r="S47" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="48" spans="2:30" x14ac:dyDescent="0.3">
       <c r="S48" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S49" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S50" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="51" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S51" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S52" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="53" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S53" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S54" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="55" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S55" s="13" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="19:19" x14ac:dyDescent="0.3">
       <c r="S56" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BBCBC4-F056-4E6C-ACB7-1B5DC3A576B9}">
-  <dimension ref="A1:AA130"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="21" max="21" width="24.21875" customWidth="1"/>
-    <col min="22" max="22" width="25.77734375" style="36" customWidth="1"/>
-    <col min="23" max="23" width="23.77734375" style="36" customWidth="1"/>
-    <col min="24" max="25" width="34.44140625" customWidth="1"/>
-    <col min="26" max="26" width="74.5546875" customWidth="1"/>
-    <col min="27" max="27" width="16.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" s="45" customFormat="1" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A1" s="46" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="26" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="U2" s="26" t="s">
-        <v>153</v>
-      </c>
-      <c r="V2" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="W2" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="X2" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="Y2" s="26" t="s">
-        <v>174</v>
-      </c>
-      <c r="Z2" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="AA2" s="26" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U3" t="s">
-        <v>0</v>
-      </c>
-      <c r="V3" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="W3" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="X3" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U4" t="s">
-        <v>79</v>
-      </c>
-      <c r="V4" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="W4" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="X4" t="s">
-        <v>158</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z4" s="29" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U5" t="s">
-        <v>80</v>
-      </c>
-      <c r="V5" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="W5" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="X5" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z5" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U6" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="W6" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="X6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z6" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U7" t="s">
-        <v>1</v>
-      </c>
-      <c r="V7" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="W7" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="X7" t="s">
-        <v>161</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z7" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="AA7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U8" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="V8" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="W8" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="X8" s="38"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U9" s="51" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="52">
-        <v>1</v>
-      </c>
-      <c r="W9" s="52">
-        <v>2</v>
-      </c>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="53"/>
-      <c r="Z9" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="AA9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U10" t="s">
-        <v>4</v>
-      </c>
-      <c r="V10" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="W10" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="X10" t="s">
-        <v>168</v>
-      </c>
-      <c r="Y10" t="s">
-        <v>179</v>
-      </c>
-      <c r="Z10" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AA10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U11" t="s">
-        <v>5</v>
-      </c>
-      <c r="V11" s="36">
-        <v>1</v>
-      </c>
-      <c r="W11" s="36">
-        <v>2</v>
-      </c>
-      <c r="X11" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>182</v>
-      </c>
-      <c r="Z11" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U12" t="s">
-        <v>11</v>
-      </c>
-      <c r="V12" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="W12" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z12" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U13" t="s">
-        <v>12</v>
-      </c>
-      <c r="V13" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="W13" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="X13" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z13" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U14" t="s">
-        <v>21</v>
-      </c>
-      <c r="V14" s="34">
-        <v>46112</v>
-      </c>
-      <c r="W14" s="34">
-        <v>46113</v>
-      </c>
-      <c r="X14" t="s">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>180</v>
-      </c>
-      <c r="Z14" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U15" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="V15" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="W15" s="52" t="s">
-        <v>88</v>
-      </c>
-      <c r="X15" s="51"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA15">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="U16" t="s">
-        <v>26</v>
-      </c>
-      <c r="V16" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="W16" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="X16" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>181</v>
-      </c>
-      <c r="Z16" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="U17" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="V17" s="52"/>
-      <c r="W17" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="X17" s="51"/>
-      <c r="Y17" s="53"/>
-      <c r="Z17" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="U18" t="s">
-        <v>17</v>
-      </c>
-      <c r="V18" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="W18" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="X18" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z18" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z19" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z20" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z21" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z22" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z23" s="32" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z24" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z25" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z26" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z27" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z28" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z29" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z30" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z31" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="21:27" x14ac:dyDescent="0.3">
-      <c r="Z32" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z33" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA33">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z34" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z35" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z36" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z37" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z38" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="AA38">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z39" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z40" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA40">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z41" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z42" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z43" s="32" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA43">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z44" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA44">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z45" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA45">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z46" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z47" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z48" s="32" t="s">
-        <v>114</v>
-      </c>
-      <c r="AA48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z49" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA49">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z50" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA50">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z51" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA51">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z52" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z53" s="32" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z54" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA54">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z55" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA55">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z56" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z57" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z58" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z59" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA59">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z60" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z61" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z62" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z63" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="AA63">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="64" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z64" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA64">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="65" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z65" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA65">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="66" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z66" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z67" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z68" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="AA68">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="69" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z69" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA69">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z70" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z71" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z72" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z73" t="s">
-        <v>124</v>
-      </c>
-      <c r="AA73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z74" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z75" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z76" s="30" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA76">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z77" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA77">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z78" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z79" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z80" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="AA80">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z81" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA81">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="82" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z82" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="AA82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z83" s="32" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA83">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z84" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA84">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="85" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z85" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA85">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z86" s="30" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z87" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA87">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z88" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA88">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="89" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z89" s="30" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z90" s="32" t="s">
-        <v>130</v>
-      </c>
-      <c r="AA90">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="91" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z91" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="AA91">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z92" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA92">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z93" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="AA93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z94" s="32" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA94">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z95" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA95">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="96" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z96" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z97" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="AA97">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="98" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z98" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA98">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="99" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z99" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA99">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="100" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z100" s="30" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z101" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA101">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z102" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA102">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="103" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z103" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z104" s="32" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA104">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="105" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z105" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="AA105">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="106" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z106" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z107" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z108" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA108">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z109" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA109">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z110" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z111" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA111">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z112" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA112">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z113" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA113">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="114" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z114" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z115" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z116" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="AA116">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="117" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z117" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z118" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z119" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA119">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="120" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z120" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z121" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="AA121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z122" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z123" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z124" s="30" t="s">
-        <v>146</v>
-      </c>
-      <c r="AA124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z125" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="AA125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z126" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="AA126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z127" s="30" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z128" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z129" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="26:27" x14ac:dyDescent="0.3">
-      <c r="Z130" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA130">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="U2:AA129" xr:uid="{80BBCBC4-F056-4E6C-ACB7-1B5DC3A576B9}"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>